--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2759,7 +2759,7 @@
         <v>19</v>
       </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2931,7 +2931,7 @@
         <v>8</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
@@ -1042,7 +1042,7 @@
         <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1171,7 +1171,7 @@
         <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2762,7 +2762,7 @@
         <v>9</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2934,7 +2934,7 @@
         <v>6</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2977,7 +2977,7 @@
         <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1039,10 +1039,10 @@
         <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1168,10 +1168,10 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2759,10 +2759,10 @@
         <v>19</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2931,10 +2931,10 @@
         <v>8</v>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2977,7 +2977,7 @@
         <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1039,10 +1039,10 @@
         <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1168,10 +1168,10 @@
         <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2759,10 +2759,10 @@
         <v>19</v>
       </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2931,10 +2931,10 @@
         <v>8</v>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2977,7 +2977,7 @@
         <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -741,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1171,7 +1171,7 @@
         <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1257,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1429,7 +1429,7 @@
         <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>4</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         <v>5</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2762,7 +2762,7 @@
         <v>9</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -2891,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2934,7 +2934,7 @@
         <v>6</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>

--- a/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
+++ b/wildlife/reports/United-Kingdom/heatmap/2025/Abingdon/Flora/heatmap.xlsx
@@ -1171,7 +1171,7 @@
         <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2762,7 +2762,7 @@
         <v>9</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2934,7 +2934,7 @@
         <v>6</v>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2977,7 +2977,7 @@
         <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
